--- a/tame_output/ON/bt/strategyON_20230904.xlsx
+++ b/tame_output/ON/bt/strategyON_20230904.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.0%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.4%</t>
+          <t>454.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13.6%</t>
+          <t>13.4%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.3%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>132.8%</t>
+          <t>132.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2023-09-03</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.4%</t>
+          <t>127.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1709"/>
+  <dimension ref="A1:G1710"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40817,7 +40817,7 @@
         <v>45171</v>
       </c>
       <c r="B1709" t="n">
-        <v>2.76312557482448</v>
+        <v>2.763430248778772</v>
       </c>
       <c r="C1709" t="n">
         <v>2.905777380171683</v>
@@ -40833,6 +40833,29 @@
       </c>
       <c r="G1709" t="n">
         <v>4.206708256987207</v>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" s="2" t="n">
+        <v>45172</v>
+      </c>
+      <c r="B1710" t="n">
+        <v>2.769035356436508</v>
+      </c>
+      <c r="C1710" t="n">
+        <v>2.904913189979939</v>
+      </c>
+      <c r="D1710" t="n">
+        <v>1.557896421996732</v>
+      </c>
+      <c r="E1710" t="n">
+        <v>3.527715334464885</v>
+      </c>
+      <c r="F1710" t="n">
+        <v>2.168218128025871</v>
+      </c>
+      <c r="G1710" t="n">
+        <v>4.205844066795463</v>
       </c>
     </row>
   </sheetData>
